--- a/AAII_Financials/Quarterly/BTI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BTI_QTR_FIN.xlsx
@@ -656,365 +656,389 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8116600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8078000</v>
+      </c>
+      <c r="F8" s="3">
         <v>9112400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9100900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>8267600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>7796600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8467400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9065100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>7797600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7792600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8815700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8445800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8540400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8314200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8907800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>17281100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>15223400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>17007600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>14254700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>15683000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>15488700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>17187900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>9876300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>9189000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>8621700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>8746700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>8424800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>9445300</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1322100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1315900</v>
+      </c>
+      <c r="F9" s="3">
         <v>1656800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1654700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1357000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1279700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1506100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1612400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1367400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1366500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1685800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1615100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1425800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1388100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1597100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2737100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2480000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2945700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2416400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2770400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>3033600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>4376900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2582900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2599900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2096900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2054300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1919900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2063400</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>6794500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6762100</v>
+      </c>
+      <c r="F10" s="3">
         <v>7455600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>7446200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>6910500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>6516900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>6961300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>7452800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>6430200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>6426000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>7129800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>6830700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>7114500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>6926100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>7310700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>14544000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>12743400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>14062000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>11838300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>12912600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>12455100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>12811000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>7293400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>6589100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>6524800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>6692400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>6504900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>7381900</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1044,55 +1068,57 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>124700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>124100</v>
+      </c>
+      <c r="F12" s="3">
         <v>123800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>123700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>119200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>112400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>132700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>142100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>106200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>106100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>136300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>130600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>123300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>120000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>104200</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>8</v>
@@ -1127,8 +1153,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1210,174 +1242,192 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>209000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>208000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-206600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-206300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>13000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>12300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>4220900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>4518800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-138400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-138300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>18037000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>17280300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>17800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>17300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>435000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>689700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>100500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>589400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>108900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>325700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>131800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>660900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>177100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>668800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>208100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>405600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>175100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>431900</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>904900</v>
+      </c>
+      <c r="E15" s="3">
+        <v>900600</v>
+      </c>
+      <c r="F15" s="3">
         <v>687800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>686900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>816600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>770000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>597200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>639300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>808800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>808300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>235000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>225100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>305000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>296900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>261500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>730700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>643900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>1172600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>590300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>707500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>545800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>675000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>452700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>471700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>303800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>352200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>293600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>420100</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1404,174 +1454,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5283300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5258100</v>
+      </c>
+      <c r="F17" s="3">
         <v>5961600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5954100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4791800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4518800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5216100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5584400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4889600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4886500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4614200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4420600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4767400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4641100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4305100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>11055800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>8900100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>11255300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>9124400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>9736000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>9581300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>11756700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>6449300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6181400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>5760800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>5964600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>5334300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>6697200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2833400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2819900</v>
+      </c>
+      <c r="F18" s="3">
         <v>3150700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>3146800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>3475800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>3277800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3251200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>3480800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>2908000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2906100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4201500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4025200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3773000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3673100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>4602700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>6225300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6323300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>5752300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>5130300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>5947000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>5907400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>5431200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>3427000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>3007600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>2861000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>2782100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>3090500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2748100</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1601,233 +1665,247 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-555900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-553300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-61900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-61800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-878900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-828800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-141500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-151500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-986400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-985800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-118500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-113500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-134100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-130500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-77100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-1004500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-626500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-730800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-603200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-601400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-624300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>32069200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>603100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>464300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1568200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>675600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1893500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>579400</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4294100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4273700</v>
+      </c>
+      <c r="F21" s="3">
         <v>3900400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>3895500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>5171300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>4876700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>3989900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>4271500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>4703200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>4700200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>4554900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4363800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>4212000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>4100500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>4941300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>6204800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>6354400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>6194100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>5117400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>6053100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>5828900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>38175400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>4482800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>3907900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>4756200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>3759000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>5243500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>3708100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>548600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>546000</v>
+      </c>
+      <c r="F22" s="3">
         <v>602300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>601500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>602100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>567800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>545200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>583700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>569300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>569000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>590400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>565600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>573800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>558600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>510300</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
@@ -1841,183 +1919,201 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC22" s="3">
         <v>382200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>379200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>385800</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2688100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2675300</v>
+      </c>
+      <c r="F23" s="3">
         <v>2883600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2879900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>3818300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3600800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1290700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1381900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>3538600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3536300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-14243100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-13645600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>3369500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3280300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>3773100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>5220800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5696800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>5021500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>4527100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>5345600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>5283100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>37500400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>4030100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>3471900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>4429200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>3075600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>4604800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2941700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>546600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>544000</v>
+      </c>
+      <c r="F24" s="3">
         <v>730100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>729200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>691200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>651800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-428200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-458400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>657800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>657400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-2636700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-2526100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>805700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>784300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>816300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1485600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1339800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1426900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>1145500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>1326000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>1496200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1099500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>905400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>888000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>885600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>808700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>938900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>957300</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2099,174 +2195,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2141400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2131200</v>
+      </c>
+      <c r="F26" s="3">
         <v>2153400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>2150700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3127100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2949000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-862600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-923500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>2880800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2879000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-11606500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-11119500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2563800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2495900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2956800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>3735200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>4357000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>3594600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3381500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>4019600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3787000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>36400900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3124800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>2583900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>3543600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>2266900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>3665900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1984400</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2097700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2087700</v>
+      </c>
+      <c r="F27" s="3">
         <v>2144700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>2142000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3075800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2900600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-904500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-968400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2825200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2823400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-11686100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-11195800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2501600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2435300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2880300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>3629000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>4256500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>3513900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3287800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3907300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3672500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>36280600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3010300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>2434900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>3453100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>2145600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>3482900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1801400</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2348,8 +2462,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2393,31 +2513,31 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>136900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>32300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>72000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>8200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>169600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-91800</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>13565200</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2431,8 +2551,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2514,8 +2640,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2597,174 +2729,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>555900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>553300</v>
+      </c>
+      <c r="F32" s="3">
         <v>61900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>61800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>878900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>828800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>141500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>151500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>986400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>985800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>118500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>113500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>134100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>130500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>77100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>1004500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>626500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>730800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>603200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>601400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>624300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-32069200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-603100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-464300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1568200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-675600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1893500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-579400</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2116200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2106200</v>
+      </c>
+      <c r="F33" s="3">
         <v>2188400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>2185700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3090800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2914800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-891400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-954300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>2838500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2836600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-11671400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-11181800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2515500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2448900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2896000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>3765900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>4288800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>3585900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3296000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>4076900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3580700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>49845800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3010300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>2434900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>3453100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>2145600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>3482900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1801400</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2846,179 +2996,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2116200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2106200</v>
+      </c>
+      <c r="F35" s="3">
         <v>2188400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>2185700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3090800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2914800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-891400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-954300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>2838500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2836600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-11671400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-11181800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2515500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2448900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2896000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>3765900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>4288800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>3585900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3296000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>4076900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3580700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>49845800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3010300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>2434900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>3453100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>2145600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>3482900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1801400</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3048,8 +3216,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3079,755 +3249,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3340900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3324900</v>
+      </c>
+      <c r="F41" s="3">
         <v>5150700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5144200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6033700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5690000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6631400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7099600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7499300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7494500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5934400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5685500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4677800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4553900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4152100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4016700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>5935000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3134300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3874700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>3174200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>2828600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>4657100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2688100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2714400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2433100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2560400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1865900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2393900</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>19800</v>
+      </c>
+      <c r="F42" s="3">
         <v>21500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>21500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>670000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>631800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>642200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>687600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>879600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>879000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>765500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>733400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>573100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>557900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>697600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>309700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>227000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>152600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>195600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>217100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>250200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>92000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>34600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>18500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>78900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>45700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>65800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>65800</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5718500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5691200</v>
+      </c>
+      <c r="F43" s="3">
         <v>5749700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>5742400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>4908900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>4629300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4595800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4920300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>4722800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4719700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4831400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4628700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>5564800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5417400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5441300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4862500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>5696800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>5230000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4739100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4467300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>5441500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>6386400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>5197800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>4868500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4487300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4356400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3414400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>3719900</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6428300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>6397700</v>
+      </c>
+      <c r="F44" s="3">
         <v>5897700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5890300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6970800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>6573700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5778900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6186800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6741100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>6736700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>6289800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6025900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>7159600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>6970000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>6832900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>7675100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>8431100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>7561400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>7858300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>7354800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>8437800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>8298200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>6892700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>7134700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>6108500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>5539400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>4959000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>5442300</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>311800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>310300</v>
+      </c>
+      <c r="F45" s="3">
         <v>251700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>251400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>426100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>401800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>246600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>264000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>216100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>216000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>248400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>238000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1203400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1171600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1442300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>554100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>264200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>392100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>217900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>224500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>262200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>329700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>463300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>485300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>711000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>298700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>454300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>402900</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15819300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15744000</v>
+      </c>
+      <c r="F46" s="3">
         <v>17071300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>17049800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19009500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17926600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17895000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>19158300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>20058900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>20046000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>18069500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17311400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>19178800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>18670800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18566200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17418100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>20554300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>16470400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>16885500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>15437800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>17220400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>19763400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>15276500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>15221300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>13818800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>12800500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>10759500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>12024900</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2457200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2445500</v>
+      </c>
+      <c r="F47" s="3">
         <v>2495300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2492100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>3110000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2932900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2563900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2744900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2602100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2600500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2659600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2548000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>2760200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>2687100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>2579700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>2636000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2978700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2630500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2764300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>3002200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>3390300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>3360900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>13633500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>12499500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>11864100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>9421000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>8967300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>3409200</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5601700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5575000</v>
+      </c>
+      <c r="F48" s="3">
         <v>6033600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>6026000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>5698000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>5373500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>5482200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>5869200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>5594800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>5591200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>5837600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>5592700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5745300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5593100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5864200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6474800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6753800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6846700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>6656500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>6302000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6454500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>6908600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>4841000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>4508900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>4232700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>3940300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>3727800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>3955600</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>115546000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>114995900</v>
+      </c>
+      <c r="F49" s="3">
         <v>117004000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>116856200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>118129900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>111400700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>118026500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>126358400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>119681000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>119603900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>121722600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>116615800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>155196900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>151086200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>155521400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>147594100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>157263400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>147390900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>145343100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>151283500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>159740000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>166678700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>16212500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>14923300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>15229300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>13611800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>13336400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>14226600</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3909,8 +4135,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3992,91 +4224,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1653200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1645300</v>
+      </c>
+      <c r="F52" s="3">
         <v>1753700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1751500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1733100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1634400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1663800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1781300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1716200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1715100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1765400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1691400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1831200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1782700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1653100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>2066600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1860900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1620500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1834300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>2497100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>2877800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2895300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2208800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1831400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1705200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1331700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>967800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>840100</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4158,91 +4402,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>143807900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>143123300</v>
+      </c>
+      <c r="F54" s="3">
         <v>147092900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>146907000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>151015200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>142412700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>148852600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>159360700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>150857500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>150760300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>151215200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>144871000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>185627300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>180710600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>185006300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>176189500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>189411100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>174959000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>173483600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>178522600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>189683100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>199606900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>52172200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>48984400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>46850100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>41105300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>37759000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>34456400</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4272,8 +4528,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4303,506 +4561,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11378500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11324400</v>
+      </c>
+      <c r="F57" s="3">
         <v>2441500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2438400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>11293300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>10650000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2139500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2290600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>11395600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>11388300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>2174300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2083100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>11712900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11402700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2243500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>12403300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>11829100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>12069300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>11434200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>12968800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>12642800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>12605800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>7919200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>9033800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>6567500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>7743700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>5837300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>7273900</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5331000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5305700</v>
+      </c>
+      <c r="F58" s="3">
         <v>4524900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>4519200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4526600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4268800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5398300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5779400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>9245900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>9239900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>5507700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5276600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6390800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6221500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5334100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>5170900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>8766100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>9382900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>10203200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>5154100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>7037500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>7674100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>7751400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3703400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>6907500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2863000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>1765800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3264300</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2234300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2223700</v>
+      </c>
+      <c r="F59" s="3">
         <v>12566600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>12550700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6095400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>5748100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>15913200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>17036600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2159800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2158400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>12265000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>11750400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2471700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2406200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>13916500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>2231600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>2398100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1903400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1546100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1796900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1683800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1802900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1898600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1864600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1763400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1140000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1067900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1008700</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18943900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>18853700</v>
+      </c>
+      <c r="F60" s="3">
         <v>19547800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19523100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>21915300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>20666900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>23464800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>25121300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>22801300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>22786600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>19963600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>19126000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>20575400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>20030400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>21510900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>19805800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>22993300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>23355600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>23183500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>19919700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>21364200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>22082800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>17569200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>14601800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>15238400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>11746600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>8671100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>11546900</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>41190100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>40994100</v>
+      </c>
+      <c r="F61" s="3">
         <v>42675600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>42621700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>43870400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>41371300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>40860300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>43744800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>41792300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>41765400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>45336800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>43434700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>47197300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>45947100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>47184800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>51091000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>53835800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>46907200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>48703800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>52802200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>57536800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>62303000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>20084200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>20306600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>19247400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>19311600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>18607600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>12876900</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4420900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4399800</v>
+      </c>
+      <c r="F62" s="3">
         <v>5040400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5034000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5248700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4949700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6250900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>6692100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1338400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1337500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1801100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1725500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2342100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2280000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1704900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>24734900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>26453300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>25086500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>24833900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>25667900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>27430000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>28926300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3988900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3723100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>4281800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3483800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2253000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2376800</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4884,8 +5180,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4967,8 +5269,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5050,91 +5358,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>79332600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>78955000</v>
+      </c>
+      <c r="F66" s="3">
         <v>82294800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>82190800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>86380300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>81459700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>86262600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>92352200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>82020000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>81967200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>83790200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>80274800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>93332100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>90860100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>93784000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>95992500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>103632300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>95669400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>97018800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>98687500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>106621100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>113626300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>41897800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>38907500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>38951100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>34722000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>29875300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>27200900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5164,8 +5484,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5247,8 +5569,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5330,8 +5658,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5413,8 +5747,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5496,91 +5836,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>30262700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>30118600</v>
+      </c>
+      <c r="F72" s="3">
         <v>36759100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>36712600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>31502900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>29708400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>32572600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>34872000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>32890200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>32869000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>40285100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>38594900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>57936700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>56402200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>61686800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>45350700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>51996000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>45511300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>44580800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>46629500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>46830800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>47467000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>4363000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>4611100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2164200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>600000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2046300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1422100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5662,8 +6014,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5745,8 +6103,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5828,91 +6192,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64188700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>63883100</v>
+      </c>
+      <c r="F76" s="3">
         <v>64503400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>64421900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>64219800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>60561500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>62149300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>66536700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>68385000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>68341000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>66956200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>64147100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>91875800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>89442300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>90810300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>80197000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>85778800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>79289600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>76464800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>79835100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>83062000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>85980700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>10274400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>10077000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>7899100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>6383300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>7883600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7255500</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5994,179 +6370,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2116200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2106200</v>
+      </c>
+      <c r="F81" s="3">
         <v>2188400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>2185700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3090800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2914800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-891400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-954300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>2838500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2836600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-11671400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-11181800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2515500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2448900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2896000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>3765900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>4288800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>3585900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3296000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>4076900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3580700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>49845800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3010300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>2434900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>3453100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>2145600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>3482900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1801400</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6196,91 +6590,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>216500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>204100</v>
+      </c>
+      <c r="F83" s="3">
         <v>85800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>91800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>205400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>205200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>219100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>73200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>236400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>230100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>216900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>88000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>223000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>241200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>255900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>984000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>657500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>1172600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>590300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>707500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>545800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>675000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>452700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>436000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>327100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>301300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>259400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>339700</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6362,8 +6764,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6445,8 +6853,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6528,8 +6942,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6611,8 +7031,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6694,91 +7120,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2256900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2246100</v>
+      </c>
+      <c r="F89" s="3">
         <v>2714000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2710600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>1581700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1491600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>4356700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>4664300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1999900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>1998700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>4674000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>4477900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>2144500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2087700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4321300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>8064100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>4322300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>8323300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>2679900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>7852500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>5135400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>5152400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2271400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>4379600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1362600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>4389000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>1784300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>3352500</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6808,91 +7246,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-88900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-88500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-301500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-301100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-70600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-66500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-231600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-248000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-73300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-73300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-222900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-213600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-69900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-68000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-255400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-587000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-168000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-581000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-208500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-674600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-272900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-839200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-263600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-573900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-155100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-429100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-271300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-546500</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6974,8 +7420,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7057,91 +7509,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-199000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-198100</v>
+      </c>
+      <c r="F94" s="3">
         <v>252400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>252000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>693200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>653800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-36300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-38900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>905500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>904900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-214600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-205600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>26100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>25400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-299400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-724300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-269200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-534800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-243600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-897800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-379400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-25821500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-395400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-517300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-284400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-984800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-4261100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-446400</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7171,91 +7635,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1751400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>1743000</v>
+      </c>
+      <c r="F96" s="3">
         <v>1805500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>1803200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>1787200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>1685400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>1667600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>1785300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>1646100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>1645000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>1678200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>1607800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>1575100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>1533400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>1505500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-3069800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-2910400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-2879900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-2667100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-2724000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-2813900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-1819800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-2901100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-1182300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-2521000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1184300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-2451900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-1160100</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7337,8 +7809,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7420,8 +7898,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7503,253 +7987,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3093400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3078700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3125800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-3121900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-2820200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2659600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-4553300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-4874700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-2121900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2120500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-4006600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-3838500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1920800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1869900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-3909300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-8874100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1193500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-8220300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2305100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-6266600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-5980600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>23023800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-2011700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-3914000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1358700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-2429900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>2164800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2575600</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-98600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-136500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-146100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-39800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-39800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-77100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-73800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-108700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-105800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>36100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>33400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>225400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>243800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-54200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-335300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>11200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-3700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-63300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>12200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-197000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-356600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-185100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>287000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-68500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-224300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-131700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-88200</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1013000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1008200</v>
+      </c>
+      <c r="F102" s="3">
         <v>-113700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-113600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-643900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-607200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-369300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-395400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>743700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>743300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>375800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>360000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>141100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>137300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>148800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1869500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2870700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-435500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>67900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>700200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-1421600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1998100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-320900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>235200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-349100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>750000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-443800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>242300</v>
       </c>
     </row>
